--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486301_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486301_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.1296</v>
+        <v>9.0718</v>
       </c>
       <c r="E2" t="n">
-        <v>7.7143</v>
+        <v>7.3791</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4153</v>
+        <v>1.6927</v>
       </c>
       <c r="G2" t="n">
         <v>4.8171</v>
@@ -610,13 +610,13 @@
         <v>0.87</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2054</v>
+        <v>0.1475</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0791</v>
+        <v>0.7439</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8738</v>
+        <v>-0.5964</v>
       </c>
       <c r="V2" t="n">
         <v>4.3247</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8878</v>
+        <v>4.3386</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8219</v>
+        <v>3.9337</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0659</v>
+        <v>0.4049</v>
       </c>
       <c r="G3" t="n">
         <v>4.4906</v>
@@ -688,13 +688,13 @@
         <v>0.6525</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.4251</v>
+        <v>-0.9743000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0601</v>
+        <v>0.1719</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.4852</v>
+        <v>-1.1461</v>
       </c>
       <c r="V3" t="n">
         <v>4.5199</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8743</v>
+        <v>1.9517</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.0325</v>
+        <v>-1.9208</v>
       </c>
       <c r="F4" t="n">
-        <v>5.9068</v>
+        <v>3.8725</v>
       </c>
       <c r="G4" t="n">
         <v>4.5156</v>
@@ -766,13 +766,13 @@
         <v>1.0875</v>
       </c>
       <c r="S4" t="n">
-        <v>2.6213</v>
+        <v>0.6988</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0601</v>
+        <v>0.1719</v>
       </c>
       <c r="U4" t="n">
-        <v>2.5612</v>
+        <v>0.5269</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0864</v>
+        <v>1.7973</v>
       </c>
       <c r="E5" t="n">
-        <v>1.619</v>
+        <v>0.8367</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4675</v>
+        <v>0.9606</v>
       </c>
       <c r="G5" t="n">
         <v>2.7463</v>
@@ -844,13 +844,13 @@
         <v>0.87</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4848</v>
+        <v>-0.7739</v>
       </c>
       <c r="T5" t="n">
-        <v>1.4132</v>
+        <v>0.6309</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.898</v>
+        <v>-1.4048</v>
       </c>
       <c r="V5" t="n">
         <v>1.13</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3172</v>
+        <v>0.2055</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4617</v>
+        <v>-0.5734</v>
       </c>
       <c r="F6" t="n">
         <v>0.7789</v>
@@ -922,10 +922,10 @@
         <v>0.2175</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0565</v>
+        <v>-0.0553</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1971</v>
+        <v>0.0853</v>
       </c>
       <c r="U6" t="n">
         <v>-0.1406</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. STILMA</t>
+          <t>S. PENO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9254</v>
+        <v>-0.9778</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2794</v>
+        <v>-0.8638</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.2048</v>
+        <v>-0.114</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1596</v>
+        <v>-0.6113</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6632</v>
+        <v>-0.0152</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5036</v>
+        <v>-0.596</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4096</v>
+        <v>-0.7268</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1857</v>
+        <v>0.0182</v>
       </c>
       <c r="L7" t="n">
-        <v>1.224</v>
+        <v>-0.7451</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5692</v>
+        <v>0.1155</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8488</v>
+        <v>-0.0335</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7204</v>
+        <v>0.149</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.0875</v>
+        <v>0.2175</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.2175</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4385</v>
+        <v>-0.584</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1971</v>
+        <v>-0.137</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.447</v>
       </c>
       <c r="V7" t="n">
-        <v>0.7602</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7602</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. PENO</t>
+          <t>M. STILMA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9778</v>
+        <v>-1.1181</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8638</v>
+        <v>1.0559</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.114</v>
+        <v>-2.174</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6113</v>
+        <v>-0.1596</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0152</v>
+        <v>-0.6632</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.596</v>
+        <v>0.5036</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7268</v>
+        <v>1.4096</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0182</v>
+        <v>0.1857</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7451</v>
+        <v>1.224</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1155</v>
+        <v>-1.5692</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0335</v>
+        <v>-0.8488</v>
       </c>
       <c r="O8" t="n">
-        <v>0.149</v>
+        <v>-0.7204</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2175</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2175</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.584</v>
+        <v>-0.6312</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.137</v>
+        <v>-0.0264</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.447</v>
+        <v>-0.6048</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.7602</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.7602</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0588</v>
+        <v>-1.2728</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6812</v>
+        <v>-1.2341</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3777</v>
+        <v>-0.0386</v>
       </c>
       <c r="G9" t="n">
         <v>0.9555</v>
@@ -1156,13 +1156,13 @@
         <v>0.435</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4696</v>
+        <v>-0.6835</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.2379</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7846</v>
+        <v>-0.4455</v>
       </c>
       <c r="V9" t="n">
         <v>0.1952</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7008</v>
+        <v>-1.6797</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8577</v>
+        <v>-2.2989</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1569</v>
+        <v>0.6193</v>
       </c>
       <c r="G10" t="n">
         <v>0.4149</v>
@@ -1234,13 +1234,13 @@
         <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.7899</v>
+        <v>-0.7688</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6165</v>
+        <v>-0.0577</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1735</v>
+        <v>-0.7111</v>
       </c>
       <c r="V10" t="n">
         <v>-0.0207</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3698</v>
+        <v>-3.0538</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.6167</v>
+        <v>-3.3931</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2469</v>
+        <v>0.3393</v>
       </c>
       <c r="G11" t="n">
         <v>-1.7114</v>
@@ -1312,13 +1312,13 @@
         <v>0.2175</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6149</v>
+        <v>-0.2989</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.4614</v>
       </c>
       <c r="U11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1625</v>
       </c>
       <c r="V11" t="n">
         <v>0.9141</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.262699999999997</v>
+        <v>9.262699999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>2.920999999999999</v>
+        <v>2.921300000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>6.3417</v>
+        <v>6.3416</v>
       </c>
       <c r="G12" t="n">
         <v>16.0442</v>
@@ -1393,10 +1393,10 @@
         <v>-3.9236</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8831999999999998</v>
+        <v>0.8834999999999997</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.807099999999999</v>
+        <v>-4.806900000000001</v>
       </c>
       <c r="V12" t="n">
         <v>12.3677</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.3377</v>
+        <v>3.251</v>
       </c>
       <c r="E13" t="n">
-        <v>3.9145</v>
+        <v>2.797</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4232</v>
+        <v>0.454</v>
       </c>
       <c r="G13" t="n">
         <v>0.9825</v>
@@ -1468,13 +1468,13 @@
         <v>1.7401</v>
       </c>
       <c r="S13" t="n">
-        <v>1.6152</v>
+        <v>0.5285</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5502</v>
+        <v>0.4326</v>
       </c>
       <c r="U13" t="n">
-        <v>0.065</v>
+        <v>0.0958</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. ARMUS</t>
+          <t>I. JAKOVICS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1826</v>
+        <v>1.0221</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8869</v>
+        <v>0.989</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2957</v>
+        <v>0.0331</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.1621</v>
+        <v>-1.1365</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.1342</v>
+        <v>-0.5476</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0279</v>
+        <v>-0.5888</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2758</v>
+        <v>0.5618</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.3523</v>
+        <v>0.7482</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0765</v>
+        <v>-0.1864</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8863</v>
+        <v>-1.6983</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7819</v>
+        <v>-1.2959</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1044</v>
+        <v>-0.4024</v>
       </c>
       <c r="P14" t="n">
-        <v>1.305</v>
+        <v>2.1751</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3926</v>
+        <v>2.1751</v>
       </c>
       <c r="S14" t="n">
-        <v>4.4534</v>
+        <v>-0.0165</v>
       </c>
       <c r="T14" t="n">
-        <v>4.534</v>
+        <v>0.2319</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0806</v>
+        <v>-0.2485</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.4138</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.2838</v>
+        <v>0.1952</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1685</v>
+        <v>0.9989</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2472</v>
+        <v>2.8002</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.0787</v>
+        <v>-1.8013</v>
       </c>
       <c r="G15" t="n">
         <v>1.4416</v>
@@ -1624,13 +1624,13 @@
         <v>2.3926</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.601</v>
+        <v>-0.7706</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2572</v>
+        <v>-0.1899</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8581</v>
+        <v>-0.5807</v>
       </c>
       <c r="V15" t="n">
         <v>-2.0647</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. KAMBA</t>
+          <t>A. KUNKEL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2208</v>
+        <v>-0.083</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2181</v>
+        <v>2.1968</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9973</v>
+        <v>-2.2797</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7131</v>
+        <v>0.8615</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1673</v>
+        <v>2.4241</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5458</v>
+        <v>-1.5626</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2863</v>
+        <v>2.6418</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5141</v>
+        <v>3.653</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.2279</v>
+        <v>-1.0112</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9994</v>
+        <v>-1.7803</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6814</v>
+        <v>-1.2289</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.318</v>
+        <v>-0.5514</v>
       </c>
       <c r="P16" t="n">
-        <v>1.0875</v>
+        <v>1.9576</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.0875</v>
+        <v>1.9576</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7811</v>
+        <v>0.2926</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7367</v>
+        <v>0.2944</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0445</v>
+        <v>-0.0018</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9347</v>
+        <v>-3.1947</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1952</v>
+        <v>-0.7395</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.13</v>
+        <v>-2.4552</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. KUNKEL</t>
+          <t>M. KAMBA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0329</v>
+        <v>-0.1145</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3085</v>
+        <v>0.8829</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.3414</v>
+        <v>-0.9973</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8615</v>
+        <v>-0.7131</v>
       </c>
       <c r="H17" t="n">
-        <v>2.4241</v>
+        <v>-0.1673</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.5626</v>
+        <v>-0.5458</v>
       </c>
       <c r="J17" t="n">
-        <v>2.6418</v>
+        <v>0.2863</v>
       </c>
       <c r="K17" t="n">
-        <v>3.653</v>
+        <v>0.5141</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.0112</v>
+        <v>-0.2279</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7803</v>
+        <v>-0.9994</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2289</v>
+        <v>-0.6814</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5514</v>
+        <v>-0.318</v>
       </c>
       <c r="P17" t="n">
-        <v>1.9576</v>
+        <v>1.0875</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9576</v>
+        <v>1.0875</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3427</v>
+        <v>0.4458</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4062</v>
+        <v>0.4014</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0635</v>
+        <v>0.0445</v>
       </c>
       <c r="V17" t="n">
-        <v>-3.1947</v>
+        <v>-0.9347</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.7395</v>
+        <v>0.1952</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.4552</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. JAKOVICS</t>
+          <t>M. ARMUS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5232</v>
+        <v>-0.4187</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4639</v>
+        <v>-0.6836</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0594</v>
+        <v>0.2649</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1365</v>
+        <v>-1.1621</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5476</v>
+        <v>-1.1342</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5888</v>
+        <v>-0.0279</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5618</v>
+        <v>-0.2758</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7482</v>
+        <v>-0.3523</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.1864</v>
+        <v>0.0765</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6983</v>
+        <v>-0.8863</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2959</v>
+        <v>-0.7819</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4024</v>
+        <v>-0.1044</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1751</v>
+        <v>1.305</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1751</v>
+        <v>2.3926</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.5618</v>
+        <v>1.8521</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.2209</v>
+        <v>1.9636</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3409</v>
+        <v>-0.1115</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-2.4138</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1952</v>
+        <v>-1.2838</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0305</v>
+        <v>-0.8223</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.701</v>
+        <v>-2.0304</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6705</v>
+        <v>1.2081</v>
       </c>
       <c r="G19" t="n">
         <v>-3.6989</v>
@@ -1936,13 +1936,13 @@
         <v>2.8276</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9283</v>
+        <v>1.1365</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2692</v>
+        <v>0.9397</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6591</v>
+        <v>0.1968</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4508</v>
+        <v>-0.9055</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.3287</v>
+        <v>-1.8758</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8779</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="G20" t="n">
         <v>-1.884</v>
@@ -2014,13 +2014,13 @@
         <v>1.9576</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4369</v>
+        <v>0.1085</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0959</v>
+        <v>0.3569</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3409</v>
+        <v>-0.2485</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. MUÑOZ BORCHERS</t>
+          <t>A. WINTERING</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3628</v>
+        <v>-2.8688</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1917</v>
+        <v>-3.6353</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1711</v>
+        <v>0.7665</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.1837</v>
+        <v>-2.0827</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4013</v>
+        <v>1.1589</v>
       </c>
       <c r="I21" t="n">
-        <v>-4.5851</v>
+        <v>-3.2416</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.5979</v>
+        <v>-1.6929</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9671999999999999</v>
+        <v>1.2108</v>
       </c>
       <c r="L21" t="n">
-        <v>-4.5651</v>
+        <v>-2.9037</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5858</v>
+        <v>-0.3898</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5659</v>
+        <v>-0.0519</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0199</v>
+        <v>-0.3379</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5225</v>
+        <v>1.305</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5225</v>
+        <v>2.3926</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6236</v>
+        <v>-0.0264</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4062</v>
+        <v>-0.1153</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2174</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.3252</v>
+        <v>-2.0647</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X21" t="n">
         <v>-1.3252</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. WINTERING</t>
+          <t>A. MUÑOZ BORCHERS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9864</v>
+        <v>-3.3936</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.7529</v>
+        <v>-3.1917</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7665</v>
+        <v>-0.2019</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.0827</v>
+        <v>-4.1837</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1589</v>
+        <v>0.4013</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.2416</v>
+        <v>-4.5851</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.6929</v>
+        <v>-3.5979</v>
       </c>
       <c r="K22" t="n">
-        <v>1.2108</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.9037</v>
+        <v>-4.5651</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3898</v>
+        <v>-0.5858</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0519</v>
+        <v>-0.5659</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3379</v>
+        <v>-0.0199</v>
       </c>
       <c r="P22" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3926</v>
+        <v>1.5225</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.144</v>
+        <v>0.5927</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2329</v>
+        <v>0.4062</v>
       </c>
       <c r="U22" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.1866</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.0647</v>
+        <v>-1.3252</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>-1.3252</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.7858</v>
+        <v>-5.9283</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.4788</v>
+        <v>-4.5906</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.307</v>
+        <v>-1.3378</v>
       </c>
       <c r="G23" t="n">
         <v>-4.469</v>
@@ -2248,13 +2248,13 @@
         <v>0.2175</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.077</v>
+        <v>-0.2196</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1971</v>
+        <v>0.0853</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2741</v>
+        <v>-0.3049</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3698</v>
@@ -2281,10 +2281,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.2628</v>
+        <v>-9.262700000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.3418</v>
+        <v>-6.341500000000001</v>
       </c>
       <c r="F24" t="n">
         <v>-2.9211</v>
@@ -2293,7 +2293,7 @@
         <v>-16.0444</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.8206000000000004</v>
+        <v>-0.8205999999999998</v>
       </c>
       <c r="I24" t="n">
         <v>-15.2237</v>
@@ -2302,7 +2302,7 @@
         <v>-4.858999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>5.918100000000001</v>
+        <v>5.918099999999999</v>
       </c>
       <c r="L24" t="n">
         <v>-10.7771</v>
@@ -2311,7 +2311,7 @@
         <v>-11.1855</v>
       </c>
       <c r="N24" t="n">
-        <v>-6.7387</v>
+        <v>-6.738700000000001</v>
       </c>
       <c r="O24" t="n">
         <v>-4.446499999999999</v>
@@ -2329,10 +2329,10 @@
         <v>3.9236</v>
       </c>
       <c r="T24" t="n">
-        <v>4.8071</v>
+        <v>4.8068</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8831999999999999</v>
+        <v>-0.8833000000000002</v>
       </c>
       <c r="V24" t="n">
         <v>-12.3676</v>
